--- a/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
+++ b/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
@@ -560,20 +560,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FedDocs</t>
+          <t>FedLC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D4" t="n">
-        <v>20.96</v>
+        <v>35.05</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F4" t="n">
-        <v>57.46</v>
+        <v>66.37</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>110.96</v>
+        <v>120.46</v>
       </c>
       <c r="J4" t="n">
-        <v>68.08</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="5">
@@ -596,20 +596,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>FedAvg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n">
-        <v>35.05</v>
+        <v>35.77</v>
       </c>
       <c r="E5" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>66.37</v>
+        <v>73.62</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -618,34 +618,34 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>120.46</v>
+        <v>121.83</v>
       </c>
       <c r="J5" t="n">
-        <v>68.37</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nonIID(0.1)</t>
+          <t>nonIID(alpha0.66)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FedAvg</t>
+          <t>FedDocs</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>35.77</v>
+        <v>14.65</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>73.62</v>
+        <v>34.69</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -654,10 +654,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>121.83</v>
+        <v>111.98</v>
       </c>
       <c r="J6" t="n">
-        <v>68.40000000000001</v>
+        <v>69.13</v>
       </c>
     </row>
   </sheetData>

--- a/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
+++ b/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(0.1)</t>
+          <t>nonIID(plus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>20.72</v>
+        <v>21.83</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="F3" t="n">
-        <v>49.23</v>
+        <v>67.02</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -546,34 +546,34 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>120.14</v>
+        <v>118.89</v>
       </c>
       <c r="J3" t="n">
-        <v>66.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nonIID(0.1)</t>
+          <t>nonIID(alpha0.66)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>FedDocs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>35.05</v>
+        <v>14.65</v>
       </c>
       <c r="E4" t="n">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>66.37</v>
+        <v>34.69</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>120.46</v>
+        <v>111.98</v>
       </c>
       <c r="J4" t="n">
-        <v>68.37</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="5">
@@ -596,20 +596,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedAvg</t>
+          <t>FedLC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>35.77</v>
+        <v>35.05</v>
       </c>
       <c r="E5" t="n">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="F5" t="n">
-        <v>73.62</v>
+        <v>66.37</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -618,34 +618,34 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>121.83</v>
+        <v>120.46</v>
       </c>
       <c r="J5" t="n">
-        <v>68.40000000000001</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nonIID(alpha0.66)</t>
+          <t>nonIID(0.1)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FedDocs</t>
+          <t>FedAvg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>14.65</v>
+        <v>35.77</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="F6" t="n">
-        <v>34.69</v>
+        <v>73.62</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -654,10 +654,46 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>111.98</v>
+        <v>121.83</v>
       </c>
       <c r="J6" t="n">
-        <v>69.13</v>
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nonIID(0.1)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2222PyramidFL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>53</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="E7" t="n">
+        <v>125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>66.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
+++ b/PK/Exp2025-Cifar10-lr0.5-Dir0.1/resnet-dir0.1baseline_300.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(plus)</t>
+          <t>nonIID(plus1)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>21.83</v>
+        <v>16.48</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>67.02</v>
+        <v>54.52</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>118.89</v>
+        <v>121.31</v>
       </c>
       <c r="J3" t="n">
-        <v>67.90000000000001</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="4">
@@ -585,7 +585,7 @@
         <v>111.98</v>
       </c>
       <c r="J4" t="n">
-        <v>69.13</v>
+        <v>68.52</v>
       </c>
     </row>
     <row r="5">
@@ -596,20 +596,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>TiFL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D5" t="n">
-        <v>35.05</v>
+        <v>32.03</v>
       </c>
       <c r="E5" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>66.37</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>120.46</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>68.37</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="6">
@@ -636,16 +636,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" t="n">
-        <v>35.77</v>
+        <v>37.41</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="F6" t="n">
-        <v>73.62</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -657,43 +657,7 @@
         <v>121.83</v>
       </c>
       <c r="J6" t="n">
-        <v>68.40000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>nonIID(0.1)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2222PyramidFL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>53</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="E7" t="n">
-        <v>125</v>
-      </c>
-      <c r="F7" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>120.14</v>
-      </c>
-      <c r="J7" t="n">
-        <v>66.90000000000001</v>
+        <v>66.75</v>
       </c>
     </row>
   </sheetData>
